--- a/outputs/32789.xlsx
+++ b/outputs/32789.xlsx
@@ -80,11 +80,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="4">
+  <numFmts count="3">
     <numFmt numFmtId="164" formatCode="General"/>
     <numFmt numFmtId="165" formatCode="m/d/yyyy"/>
     <numFmt numFmtId="166" formatCode="0%"/>
-    <numFmt numFmtId="167" formatCode="0"/>
   </numFmts>
   <fonts count="8">
     <font>
@@ -255,123 +254,123 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="2" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="4" fillId="2" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="5" fillId="4" borderId="0" xfId="19" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="166" fontId="5" fillId="4" borderId="0" xfId="19" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="5" fillId="0" borderId="0" xfId="19" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="166" fontId="5" fillId="0" borderId="0" xfId="19" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="6" fillId="0" borderId="0" xfId="19" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="166" fontId="6" fillId="0" borderId="0" xfId="19" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="3" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="4" fillId="3" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="4" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="4" fillId="4" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="4" fillId="5" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="165" fontId="4" fillId="5" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="167" fontId="5" fillId="0" borderId="0" xfId="19" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="false" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="4" fillId="0" borderId="0" xfId="19" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="166" fontId="4" fillId="0" borderId="0" xfId="19" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="19" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="19" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="5" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="165" fontId="0" fillId="5" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="4" xfId="19" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="4" xfId="19" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="3" xfId="19" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="3" xfId="19" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="4" fillId="0" borderId="3" xfId="19" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="3" xfId="19" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1488,176 +1487,176 @@
   <dimension ref="A1:BR82"/>
   <sheetFormatPr defaultColWidth="9.16796875" defaultRowHeight="12" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="10.75"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="11.75"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="7.42"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="9.58"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="8.83"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="13.83"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="12.42"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="13.16"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="9" style="0" width="15.58"/>
-    <col collapsed="false" customWidth="true" hidden="true" outlineLevel="0" max="53" min="12" style="0" width="9"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="56" min="56" style="1" width="10.75"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="58" min="57" style="1" width="6.75"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="60" min="59" style="1" width="10.83"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="61" min="61" style="1" width="6"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="62" min="62" style="1" width="6.58"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="63" min="63" style="1" width="6"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="64" min="64" style="1" width="6.58"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="65" min="65" style="1" width="6"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="66" min="66" style="1" width="6.58"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="67" min="67" style="1" width="6"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="68" min="68" style="1" width="6.58"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="69" min="69" style="1" width="6"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="70" min="70" style="1" width="6.58"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="10.75"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="11.75"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="7.42"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="9.58"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="8.83"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="13.83"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="1" width="12.42"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="1" width="13.16"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="9" style="1" width="15.58"/>
+    <col collapsed="false" customWidth="true" hidden="true" outlineLevel="0" max="53" min="12" style="1" width="9"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="56" min="56" style="2" width="10.75"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="58" min="57" style="2" width="6.75"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="60" min="59" style="2" width="10.83"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="61" min="61" style="2" width="6"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="62" min="62" style="2" width="6.58"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="63" min="63" style="2" width="6"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="64" min="64" style="2" width="6.58"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="65" min="65" style="2" width="6"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="66" min="66" style="2" width="6.58"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="67" min="67" style="2" width="6"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="68" min="68" style="2" width="6.58"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="69" min="69" style="2" width="6"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="70" min="70" style="2" width="6.58"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="2"/>
-      <c r="BE1" s="3"/>
-      <c r="BF1" s="3"/>
-      <c r="BG1" s="3"/>
-      <c r="BH1" s="3"/>
-      <c r="BI1" s="3"/>
-      <c r="BJ1" s="3"/>
-      <c r="BK1" s="3"/>
-      <c r="BL1" s="3"/>
-      <c r="BM1" s="3"/>
-      <c r="BN1" s="3"/>
-      <c r="BO1" s="3"/>
-      <c r="BP1" s="3"/>
-      <c r="BQ1" s="3"/>
-      <c r="BR1" s="3"/>
+      <c r="A1" s="3"/>
+      <c r="BE1" s="4"/>
+      <c r="BF1" s="4"/>
+      <c r="BG1" s="4"/>
+      <c r="BH1" s="4"/>
+      <c r="BI1" s="4"/>
+      <c r="BJ1" s="4"/>
+      <c r="BK1" s="4"/>
+      <c r="BL1" s="4"/>
+      <c r="BM1" s="4"/>
+      <c r="BN1" s="4"/>
+      <c r="BO1" s="4"/>
+      <c r="BP1" s="4"/>
+      <c r="BQ1" s="4"/>
+      <c r="BR1" s="4"/>
     </row>
     <row r="2" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="4"/>
-      <c r="B2" s="5" t="s">
+      <c r="A2" s="5"/>
+      <c r="B2" s="6" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="5"/>
-      <c r="D2" s="5"/>
-      <c r="E2" s="5"/>
-      <c r="F2" s="5"/>
-      <c r="G2" s="5"/>
-      <c r="H2" s="5"/>
-      <c r="I2" s="5"/>
-      <c r="BE2" s="6" t="s">
+      <c r="C2" s="6"/>
+      <c r="D2" s="6"/>
+      <c r="E2" s="6"/>
+      <c r="F2" s="6"/>
+      <c r="G2" s="6"/>
+      <c r="H2" s="6"/>
+      <c r="I2" s="6"/>
+      <c r="BE2" s="7" t="s">
         <v>1</v>
       </c>
-      <c r="BF2" s="6"/>
-      <c r="BG2" s="7" t="s">
+      <c r="BF2" s="7"/>
+      <c r="BG2" s="8" t="s">
         <v>2</v>
       </c>
-      <c r="BH2" s="7" t="s">
+      <c r="BH2" s="8" t="s">
         <v>2</v>
       </c>
-      <c r="BI2" s="6" t="s">
+      <c r="BI2" s="7" t="s">
         <v>3</v>
       </c>
-      <c r="BJ2" s="6"/>
-      <c r="BK2" s="6" t="s">
+      <c r="BJ2" s="7"/>
+      <c r="BK2" s="7" t="s">
         <v>4</v>
       </c>
-      <c r="BL2" s="6"/>
-      <c r="BM2" s="6" t="s">
+      <c r="BL2" s="7"/>
+      <c r="BM2" s="7" t="s">
         <v>5</v>
       </c>
-      <c r="BN2" s="6"/>
-      <c r="BO2" s="6" t="s">
+      <c r="BN2" s="7"/>
+      <c r="BO2" s="7" t="s">
         <v>6</v>
       </c>
-      <c r="BP2" s="6"/>
-      <c r="BQ2" s="6"/>
-      <c r="BR2" s="6"/>
+      <c r="BP2" s="7"/>
+      <c r="BQ2" s="7"/>
+      <c r="BR2" s="7"/>
     </row>
     <row r="3" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="8" t="s">
+      <c r="A3" s="9" t="s">
         <v>7</v>
       </c>
-      <c r="B3" s="9" t="s">
+      <c r="B3" s="10" t="s">
         <v>8</v>
       </c>
-      <c r="C3" s="10" t="s">
+      <c r="C3" s="11" t="s">
         <v>9</v>
       </c>
-      <c r="D3" s="11" t="s">
+      <c r="D3" s="12" t="s">
         <v>10</v>
       </c>
-      <c r="E3" s="9" t="s">
+      <c r="E3" s="10" t="s">
         <v>11</v>
       </c>
-      <c r="F3" s="12" t="s">
+      <c r="F3" s="13" t="s">
         <v>12</v>
       </c>
-      <c r="G3" s="13" t="s">
+      <c r="G3" s="14" t="s">
         <v>13</v>
       </c>
-      <c r="H3" s="13" t="s">
+      <c r="H3" s="14" t="s">
         <v>14</v>
       </c>
-      <c r="I3" s="12" t="s">
+      <c r="I3" s="13" t="s">
         <v>15</v>
       </c>
-      <c r="BD3" s="1" t="s">
+      <c r="BD3" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="BE3" s="14" t="s">
+      <c r="BE3" s="15" t="s">
         <v>9</v>
       </c>
-      <c r="BF3" s="15" t="s">
+      <c r="BF3" s="16" t="s">
         <v>10</v>
       </c>
-      <c r="BG3" s="16" t="s">
+      <c r="BG3" s="17" t="s">
         <v>9</v>
       </c>
-      <c r="BH3" s="17" t="s">
+      <c r="BH3" s="18" t="s">
         <v>10</v>
       </c>
-      <c r="BI3" s="14" t="s">
+      <c r="BI3" s="15" t="s">
         <v>9</v>
       </c>
-      <c r="BJ3" s="15" t="s">
+      <c r="BJ3" s="16" t="s">
         <v>10</v>
       </c>
-      <c r="BK3" s="14" t="s">
+      <c r="BK3" s="15" t="s">
         <v>9</v>
       </c>
-      <c r="BL3" s="15" t="s">
+      <c r="BL3" s="16" t="s">
         <v>10</v>
       </c>
-      <c r="BM3" s="14" t="s">
+      <c r="BM3" s="15" t="s">
         <v>9</v>
       </c>
-      <c r="BN3" s="15" t="s">
+      <c r="BN3" s="16" t="s">
         <v>10</v>
       </c>
-      <c r="BO3" s="14" t="s">
+      <c r="BO3" s="15" t="s">
         <v>9</v>
       </c>
-      <c r="BP3" s="15" t="s">
+      <c r="BP3" s="16" t="s">
         <v>10</v>
       </c>
-      <c r="BQ3" s="14" t="s">
+      <c r="BQ3" s="15" t="s">
         <v>9</v>
       </c>
-      <c r="BR3" s="15" t="s">
+      <c r="BR3" s="16" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="18" t="n">
+      <c r="A4" s="19" t="n">
         <v>45215</v>
       </c>
-      <c r="B4" s="3" t="n">
+      <c r="B4" s="4" t="n">
         <v>167</v>
       </c>
-      <c r="C4" s="9" t="n">
+      <c r="C4" s="10" t="n">
         <f aca="false">IFERROR(INDEX($BE$3:$BV$81,MATCH($A4,$BD$3:$BD$81,0),MATCH(_xlfn.CONCAT(B$2),$BE$2:$BV$2,0)),"-")</f>
         <v>6</v>
       </c>
-      <c r="D4" s="19" t="n">
-        <f aca="false">IFERROR(INDEX($BE$3:$BV$81,MATCH($A4,$BD$3:$BD$81,0),MATCH(1,INDEX(($BE$2:$BV$2=B$2)*($BE$3:$BV$3=D$3),0),0)),"-")</f>
+      <c r="D4" s="13" t="n">
+        <f aca="false">IFERROR(INDEX($BE$3:$BV$81,MATCH($A4,$BD$3:$BD$81,0),MATCH(1,INDEX(($BE$2:$BV$2=_xlfn.CONCAT(B$2))*($BE$3:$BV$3=D$3),0),0)),"-")</f>
         <v>8</v>
       </c>
       <c r="E4" s="20" t="n">
@@ -1678,58 +1677,58 @@
       <c r="BD4" s="23" t="n">
         <v>45215</v>
       </c>
-      <c r="BE4" s="14" t="n">
+      <c r="BE4" s="15" t="n">
         <v>5</v>
       </c>
-      <c r="BF4" s="15" t="n">
+      <c r="BF4" s="16" t="n">
         <v>7</v>
       </c>
-      <c r="BG4" s="14" t="n">
+      <c r="BG4" s="15" t="n">
         <v>6</v>
       </c>
-      <c r="BH4" s="15" t="n">
+      <c r="BH4" s="16" t="n">
         <v>8</v>
       </c>
-      <c r="BI4" s="14" t="n">
+      <c r="BI4" s="15" t="n">
         <v>7</v>
       </c>
-      <c r="BJ4" s="15" t="n">
+      <c r="BJ4" s="16" t="n">
         <v>9</v>
       </c>
-      <c r="BK4" s="14" t="n">
+      <c r="BK4" s="15" t="n">
         <v>8</v>
       </c>
-      <c r="BL4" s="15" t="n">
+      <c r="BL4" s="16" t="n">
         <v>10</v>
       </c>
-      <c r="BM4" s="14" t="n">
+      <c r="BM4" s="15" t="n">
         <v>9</v>
       </c>
-      <c r="BN4" s="15" t="n">
+      <c r="BN4" s="16" t="n">
         <v>11</v>
       </c>
-      <c r="BO4" s="14" t="n">
+      <c r="BO4" s="15" t="n">
         <v>10</v>
       </c>
-      <c r="BP4" s="15" t="n">
+      <c r="BP4" s="16" t="n">
         <v>12</v>
       </c>
-      <c r="BQ4" s="14"/>
-      <c r="BR4" s="15"/>
+      <c r="BQ4" s="15"/>
+      <c r="BR4" s="16"/>
     </row>
     <row r="5" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="24" t="n">
         <v>45222</v>
       </c>
-      <c r="B5" s="3" t="n">
+      <c r="B5" s="4" t="n">
         <v>169</v>
       </c>
-      <c r="C5" s="9" t="n">
+      <c r="C5" s="10" t="n">
         <f aca="false">IFERROR(INDEX($BE$3:$BV$81,MATCH($A5,$BD$3:$BD$81,0),MATCH(_xlfn.CONCAT(B$2),$BE$2:$BV$2,0)),"-")</f>
         <v>7</v>
       </c>
-      <c r="D5" s="19" t="n">
-        <f aca="false">IFERROR(INDEX($BE$3:$BV$81,MATCH($A5,$BD$3:$BD$81,0),MATCH(1,INDEX(($BE$2:$BV$2=B$2)*($BE$3:$BV$3=D$3),0),0)),"-")</f>
+      <c r="D5" s="13" t="n">
+        <f aca="false">IFERROR(INDEX($BE$3:$BV$81,MATCH($A5,$BD$3:$BD$81,0),MATCH(1,INDEX(($BE$2:$BV$2=_xlfn.CONCAT(B$2))*($BE$3:$BV$3=D$3),0),0)),"-")</f>
         <v>9</v>
       </c>
       <c r="E5" s="20" t="n">
@@ -1750,58 +1749,58 @@
       <c r="BD5" s="25" t="n">
         <v>45222</v>
       </c>
-      <c r="BE5" s="14" t="n">
+      <c r="BE5" s="15" t="n">
         <v>6</v>
       </c>
-      <c r="BF5" s="15" t="n">
+      <c r="BF5" s="16" t="n">
         <v>8</v>
       </c>
-      <c r="BG5" s="14" t="n">
+      <c r="BG5" s="15" t="n">
         <v>7</v>
       </c>
-      <c r="BH5" s="15" t="n">
+      <c r="BH5" s="16" t="n">
         <v>9</v>
       </c>
-      <c r="BI5" s="14" t="n">
+      <c r="BI5" s="15" t="n">
         <v>8</v>
       </c>
-      <c r="BJ5" s="15" t="n">
+      <c r="BJ5" s="16" t="n">
         <v>10</v>
       </c>
-      <c r="BK5" s="14" t="n">
+      <c r="BK5" s="15" t="n">
         <v>9</v>
       </c>
-      <c r="BL5" s="15" t="n">
+      <c r="BL5" s="16" t="n">
         <v>11</v>
       </c>
-      <c r="BM5" s="14" t="n">
+      <c r="BM5" s="15" t="n">
         <v>10</v>
       </c>
-      <c r="BN5" s="15" t="n">
+      <c r="BN5" s="16" t="n">
         <v>12</v>
       </c>
-      <c r="BO5" s="14" t="n">
+      <c r="BO5" s="15" t="n">
         <v>11</v>
       </c>
-      <c r="BP5" s="15" t="n">
+      <c r="BP5" s="16" t="n">
         <v>13</v>
       </c>
-      <c r="BQ5" s="14"/>
-      <c r="BR5" s="15"/>
+      <c r="BQ5" s="15"/>
+      <c r="BR5" s="16"/>
     </row>
     <row r="6" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="24" t="n">
         <v>45229</v>
       </c>
-      <c r="B6" s="3" t="n">
+      <c r="B6" s="4" t="n">
         <v>171</v>
       </c>
-      <c r="C6" s="9" t="n">
+      <c r="C6" s="10" t="n">
         <f aca="false">IFERROR(INDEX($BE$3:$BV$81,MATCH($A6,$BD$3:$BD$81,0),MATCH(_xlfn.CONCAT(B$2),$BE$2:$BV$2,0)),"-")</f>
         <v>8</v>
       </c>
-      <c r="D6" s="19" t="n">
-        <f aca="false">IFERROR(INDEX($BE$3:$BV$81,MATCH($A6,$BD$3:$BD$81,0),MATCH(1,INDEX(($BE$2:$BV$2=B$2)*($BE$3:$BV$3=D$3),0),0)),"-")</f>
+      <c r="D6" s="13" t="n">
+        <f aca="false">IFERROR(INDEX($BE$3:$BV$81,MATCH($A6,$BD$3:$BD$81,0),MATCH(1,INDEX(($BE$2:$BV$2=_xlfn.CONCAT(B$2))*($BE$3:$BV$3=D$3),0),0)),"-")</f>
         <v>10</v>
       </c>
       <c r="E6" s="20" t="n">
@@ -1822,58 +1821,58 @@
       <c r="BD6" s="25" t="n">
         <v>45229</v>
       </c>
-      <c r="BE6" s="14" t="n">
+      <c r="BE6" s="15" t="n">
         <v>7</v>
       </c>
-      <c r="BF6" s="15" t="n">
+      <c r="BF6" s="16" t="n">
         <v>9</v>
       </c>
-      <c r="BG6" s="14" t="n">
+      <c r="BG6" s="15" t="n">
         <v>8</v>
       </c>
-      <c r="BH6" s="15" t="n">
+      <c r="BH6" s="16" t="n">
         <v>10</v>
       </c>
-      <c r="BI6" s="14" t="n">
+      <c r="BI6" s="15" t="n">
         <v>9</v>
       </c>
-      <c r="BJ6" s="15" t="n">
+      <c r="BJ6" s="16" t="n">
         <v>11</v>
       </c>
-      <c r="BK6" s="14" t="n">
+      <c r="BK6" s="15" t="n">
         <v>10</v>
       </c>
-      <c r="BL6" s="15" t="n">
+      <c r="BL6" s="16" t="n">
         <v>12</v>
       </c>
-      <c r="BM6" s="14" t="n">
+      <c r="BM6" s="15" t="n">
         <v>11</v>
       </c>
-      <c r="BN6" s="15" t="n">
+      <c r="BN6" s="16" t="n">
         <v>13</v>
       </c>
-      <c r="BO6" s="14" t="n">
+      <c r="BO6" s="15" t="n">
         <v>12</v>
       </c>
-      <c r="BP6" s="15" t="n">
+      <c r="BP6" s="16" t="n">
         <v>14</v>
       </c>
-      <c r="BQ6" s="14"/>
-      <c r="BR6" s="15"/>
+      <c r="BQ6" s="15"/>
+      <c r="BR6" s="16"/>
     </row>
     <row r="7" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="24" t="n">
         <v>45236</v>
       </c>
-      <c r="B7" s="3" t="n">
+      <c r="B7" s="4" t="n">
         <v>173</v>
       </c>
-      <c r="C7" s="9" t="n">
+      <c r="C7" s="10" t="n">
         <f aca="false">IFERROR(INDEX($BE$3:$BV$81,MATCH($A7,$BD$3:$BD$81,0),MATCH(_xlfn.CONCAT(B$2),$BE$2:$BV$2,0)),"-")</f>
         <v>9</v>
       </c>
-      <c r="D7" s="19" t="n">
-        <f aca="false">IFERROR(INDEX($BE$3:$BV$81,MATCH($A7,$BD$3:$BD$81,0),MATCH(1,INDEX(($BE$2:$BV$2=B$2)*($BE$3:$BV$3=D$3),0),0)),"-")</f>
+      <c r="D7" s="13" t="n">
+        <f aca="false">IFERROR(INDEX($BE$3:$BV$81,MATCH($A7,$BD$3:$BD$81,0),MATCH(1,INDEX(($BE$2:$BV$2=_xlfn.CONCAT(B$2))*($BE$3:$BV$3=D$3),0),0)),"-")</f>
         <v>11</v>
       </c>
       <c r="E7" s="20" t="n">
@@ -1894,52 +1893,52 @@
       <c r="BD7" s="25" t="n">
         <v>45236</v>
       </c>
-      <c r="BE7" s="14" t="n">
+      <c r="BE7" s="15" t="n">
         <v>8</v>
       </c>
-      <c r="BF7" s="15" t="n">
+      <c r="BF7" s="16" t="n">
         <v>10</v>
       </c>
-      <c r="BG7" s="14" t="n">
+      <c r="BG7" s="15" t="n">
         <v>9</v>
       </c>
-      <c r="BH7" s="15" t="n">
+      <c r="BH7" s="16" t="n">
         <v>11</v>
       </c>
-      <c r="BI7" s="14" t="n">
+      <c r="BI7" s="15" t="n">
         <v>10</v>
       </c>
-      <c r="BJ7" s="15" t="n">
+      <c r="BJ7" s="16" t="n">
         <v>12</v>
       </c>
-      <c r="BK7" s="14" t="n">
+      <c r="BK7" s="15" t="n">
         <v>11</v>
       </c>
-      <c r="BL7" s="15" t="n">
+      <c r="BL7" s="16" t="n">
         <v>13</v>
       </c>
-      <c r="BM7" s="14" t="n">
+      <c r="BM7" s="15" t="n">
         <v>12</v>
       </c>
-      <c r="BN7" s="15" t="n">
+      <c r="BN7" s="16" t="n">
         <v>14</v>
       </c>
-      <c r="BO7" s="14" t="n">
+      <c r="BO7" s="15" t="n">
         <v>13</v>
       </c>
-      <c r="BP7" s="15" t="n">
+      <c r="BP7" s="16" t="n">
         <v>15</v>
       </c>
-      <c r="BQ7" s="14"/>
-      <c r="BR7" s="15"/>
+      <c r="BQ7" s="15"/>
+      <c r="BR7" s="16"/>
     </row>
     <row r="8" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="24" t="n">
         <v>45243</v>
       </c>
-      <c r="B8" s="3"/>
-      <c r="C8" s="9"/>
-      <c r="D8" s="12"/>
+      <c r="B8" s="4"/>
+      <c r="C8" s="10"/>
+      <c r="D8" s="13"/>
       <c r="E8" s="20"/>
       <c r="F8" s="21" t="str">
         <f aca="false">IF(AND(NOT(ISBLANK(E8)),B8&gt;0,$AW10&gt;0),IFERROR(E8/B8,""),"")</f>
@@ -1960,52 +1959,52 @@
       <c r="BD8" s="25" t="n">
         <v>45243</v>
       </c>
-      <c r="BE8" s="14" t="n">
+      <c r="BE8" s="15" t="n">
         <v>9</v>
       </c>
-      <c r="BF8" s="15" t="n">
+      <c r="BF8" s="16" t="n">
         <v>11</v>
       </c>
-      <c r="BG8" s="14" t="n">
+      <c r="BG8" s="15" t="n">
         <v>10</v>
       </c>
-      <c r="BH8" s="15" t="n">
+      <c r="BH8" s="16" t="n">
         <v>12</v>
       </c>
-      <c r="BI8" s="14" t="n">
+      <c r="BI8" s="15" t="n">
         <v>11</v>
       </c>
-      <c r="BJ8" s="15" t="n">
+      <c r="BJ8" s="16" t="n">
         <v>13</v>
       </c>
-      <c r="BK8" s="14" t="n">
+      <c r="BK8" s="15" t="n">
         <v>12</v>
       </c>
-      <c r="BL8" s="15" t="n">
+      <c r="BL8" s="16" t="n">
         <v>14</v>
       </c>
-      <c r="BM8" s="14" t="n">
+      <c r="BM8" s="15" t="n">
         <v>13</v>
       </c>
-      <c r="BN8" s="15" t="n">
+      <c r="BN8" s="16" t="n">
         <v>15</v>
       </c>
-      <c r="BO8" s="14" t="n">
+      <c r="BO8" s="15" t="n">
         <v>14</v>
       </c>
-      <c r="BP8" s="15" t="n">
+      <c r="BP8" s="16" t="n">
         <v>16</v>
       </c>
-      <c r="BQ8" s="14"/>
-      <c r="BR8" s="15"/>
+      <c r="BQ8" s="15"/>
+      <c r="BR8" s="16"/>
     </row>
     <row r="9" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="24" t="n">
         <v>45250</v>
       </c>
-      <c r="B9" s="3"/>
-      <c r="C9" s="9"/>
-      <c r="D9" s="12"/>
+      <c r="B9" s="4"/>
+      <c r="C9" s="10"/>
+      <c r="D9" s="13"/>
       <c r="E9" s="20"/>
       <c r="F9" s="21" t="str">
         <f aca="false">IF(AND(NOT(ISBLANK(E9)),B9&gt;0,$AW11&gt;0),IFERROR(E9/B9,""),"")</f>
@@ -2026,48 +2025,48 @@
       <c r="BD9" s="25" t="n">
         <v>45243</v>
       </c>
-      <c r="BE9" s="14" t="n">
+      <c r="BE9" s="15" t="n">
         <v>9</v>
       </c>
-      <c r="BF9" s="15" t="n">
+      <c r="BF9" s="16" t="n">
         <v>11</v>
       </c>
-      <c r="BG9" s="14" t="n">
+      <c r="BG9" s="15" t="n">
         <v>10</v>
       </c>
-      <c r="BH9" s="15" t="n">
+      <c r="BH9" s="16" t="n">
         <v>12</v>
       </c>
-      <c r="BI9" s="14" t="n">
+      <c r="BI9" s="15" t="n">
         <v>11</v>
       </c>
-      <c r="BJ9" s="15" t="n">
+      <c r="BJ9" s="16" t="n">
         <v>13</v>
       </c>
-      <c r="BK9" s="14" t="n">
+      <c r="BK9" s="15" t="n">
         <v>12</v>
       </c>
-      <c r="BL9" s="15" t="n">
+      <c r="BL9" s="16" t="n">
         <v>14</v>
       </c>
-      <c r="BM9" s="14" t="n">
+      <c r="BM9" s="15" t="n">
         <v>13</v>
       </c>
-      <c r="BN9" s="15" t="n">
+      <c r="BN9" s="16" t="n">
         <v>15</v>
       </c>
-      <c r="BO9" s="14"/>
-      <c r="BP9" s="15"/>
-      <c r="BQ9" s="14"/>
-      <c r="BR9" s="15"/>
+      <c r="BO9" s="15"/>
+      <c r="BP9" s="16"/>
+      <c r="BQ9" s="15"/>
+      <c r="BR9" s="16"/>
     </row>
     <row r="10" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="24" t="n">
         <v>45257</v>
       </c>
-      <c r="B10" s="3"/>
-      <c r="C10" s="9"/>
-      <c r="D10" s="12"/>
+      <c r="B10" s="4"/>
+      <c r="C10" s="10"/>
+      <c r="D10" s="13"/>
       <c r="E10" s="20"/>
       <c r="F10" s="21" t="str">
         <f aca="false">IF(AND(NOT(ISBLANK(E10)),B10&gt;0,$AW12&gt;0),IFERROR(E10/B10,""),"")</f>
@@ -2086,28 +2085,28 @@
         <v/>
       </c>
       <c r="BD10" s="25"/>
-      <c r="BE10" s="14"/>
-      <c r="BF10" s="15"/>
-      <c r="BG10" s="14"/>
-      <c r="BH10" s="15"/>
-      <c r="BI10" s="14"/>
-      <c r="BJ10" s="15"/>
-      <c r="BK10" s="14"/>
-      <c r="BL10" s="15"/>
-      <c r="BM10" s="14"/>
+      <c r="BE10" s="15"/>
+      <c r="BF10" s="16"/>
+      <c r="BG10" s="15"/>
+      <c r="BH10" s="16"/>
+      <c r="BI10" s="15"/>
+      <c r="BJ10" s="16"/>
+      <c r="BK10" s="15"/>
+      <c r="BL10" s="16"/>
+      <c r="BM10" s="15"/>
       <c r="BN10" s="26"/>
-      <c r="BO10" s="14"/>
-      <c r="BP10" s="15"/>
-      <c r="BQ10" s="14"/>
-      <c r="BR10" s="15"/>
+      <c r="BO10" s="15"/>
+      <c r="BP10" s="16"/>
+      <c r="BQ10" s="15"/>
+      <c r="BR10" s="16"/>
     </row>
     <row r="11" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="24" t="n">
         <v>45264</v>
       </c>
-      <c r="B11" s="3"/>
-      <c r="C11" s="9"/>
-      <c r="D11" s="12"/>
+      <c r="B11" s="4"/>
+      <c r="C11" s="10"/>
+      <c r="D11" s="13"/>
       <c r="E11" s="20"/>
       <c r="F11" s="21" t="str">
         <f aca="false">IF(AND(NOT(ISBLANK(E11)),B11&gt;0,$AW13&gt;0),IFERROR(E11/B11,""),"")</f>
@@ -2145,9 +2144,9 @@
       <c r="A12" s="24" t="n">
         <v>45271</v>
       </c>
-      <c r="B12" s="3"/>
-      <c r="C12" s="9"/>
-      <c r="D12" s="12"/>
+      <c r="B12" s="4"/>
+      <c r="C12" s="10"/>
+      <c r="D12" s="13"/>
       <c r="E12" s="20"/>
       <c r="F12" s="21" t="str">
         <f aca="false">IF(AND(NOT(ISBLANK(E12)),B12&gt;0,$AW14&gt;0),IFERROR(E12/B12,""),"")</f>
@@ -2185,9 +2184,9 @@
       <c r="A13" s="24" t="n">
         <v>45278</v>
       </c>
-      <c r="B13" s="3"/>
-      <c r="C13" s="9"/>
-      <c r="D13" s="12"/>
+      <c r="B13" s="4"/>
+      <c r="C13" s="10"/>
+      <c r="D13" s="13"/>
       <c r="E13" s="20"/>
       <c r="F13" s="21" t="str">
         <f aca="false">IF(AND(NOT(ISBLANK(E13)),B13&gt;0,$AW15&gt;0),IFERROR(E13/B13,""),"")</f>
@@ -2225,12 +2224,12 @@
       <c r="A14" s="24" t="n">
         <v>45285</v>
       </c>
-      <c r="B14" s="3" t="str">
+      <c r="B14" s="4" t="str">
         <f aca="false">IF(IFERROR(INDEX('[1]UPS &amp; Billing Data'!$B$3:$BL$81,MATCH($A16,'[1]UPS &amp; Billing Data'!$A$3:$A$70,0),MATCH(_xlfn.CONCAT("Total ",#ref!),'[1]UPS &amp; Billing Data'!$B$2:$BL$2,0)),"")=0,"",IFERROR(INDEX('[1]UPS &amp; Billing Data'!$B$3:$BL$81,MATCH($A16,'[1]UPS &amp; Billing Data'!$A$3:$A$70,0),MATCH(_xlfn.CONCAT("Total ",#ref!),'[1]UPS &amp; Billing Data'!$B$2:$BL$2,0)),""))</f>
         <v/>
       </c>
-      <c r="C14" s="9"/>
-      <c r="D14" s="12"/>
+      <c r="C14" s="10"/>
+      <c r="D14" s="13"/>
       <c r="E14" s="20"/>
       <c r="F14" s="21" t="str">
         <f aca="false">IF(AND(NOT(ISBLANK(E14)),B14&gt;0,$AW16&gt;0),IFERROR(E14/B14,""),"")</f>
@@ -2283,20 +2282,20 @@
     </row>
     <row r="16" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="BD16" s="25"/>
-      <c r="BE16" s="14"/>
-      <c r="BF16" s="15"/>
-      <c r="BG16" s="14"/>
-      <c r="BH16" s="15"/>
-      <c r="BI16" s="14"/>
-      <c r="BJ16" s="15"/>
-      <c r="BK16" s="14"/>
-      <c r="BL16" s="15"/>
-      <c r="BM16" s="14"/>
-      <c r="BN16" s="15"/>
-      <c r="BO16" s="14"/>
-      <c r="BP16" s="15"/>
-      <c r="BQ16" s="14"/>
-      <c r="BR16" s="15"/>
+      <c r="BE16" s="15"/>
+      <c r="BF16" s="16"/>
+      <c r="BG16" s="15"/>
+      <c r="BH16" s="16"/>
+      <c r="BI16" s="15"/>
+      <c r="BJ16" s="16"/>
+      <c r="BK16" s="15"/>
+      <c r="BL16" s="16"/>
+      <c r="BM16" s="15"/>
+      <c r="BN16" s="16"/>
+      <c r="BO16" s="15"/>
+      <c r="BP16" s="16"/>
+      <c r="BQ16" s="15"/>
+      <c r="BR16" s="16"/>
     </row>
     <row r="17" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="BD17" s="25"/>
@@ -2555,20 +2554,20 @@
     </row>
     <row r="32" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="BD32" s="25"/>
-      <c r="BE32" s="14"/>
-      <c r="BF32" s="15"/>
-      <c r="BG32" s="14"/>
-      <c r="BH32" s="15"/>
-      <c r="BI32" s="14"/>
-      <c r="BJ32" s="15"/>
-      <c r="BK32" s="14"/>
-      <c r="BL32" s="15"/>
-      <c r="BM32" s="14"/>
-      <c r="BN32" s="15"/>
-      <c r="BO32" s="14"/>
-      <c r="BP32" s="15"/>
-      <c r="BQ32" s="14"/>
-      <c r="BR32" s="15"/>
+      <c r="BE32" s="15"/>
+      <c r="BF32" s="16"/>
+      <c r="BG32" s="15"/>
+      <c r="BH32" s="16"/>
+      <c r="BI32" s="15"/>
+      <c r="BJ32" s="16"/>
+      <c r="BK32" s="15"/>
+      <c r="BL32" s="16"/>
+      <c r="BM32" s="15"/>
+      <c r="BN32" s="16"/>
+      <c r="BO32" s="15"/>
+      <c r="BP32" s="16"/>
+      <c r="BQ32" s="15"/>
+      <c r="BR32" s="16"/>
     </row>
     <row r="33" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="BE33" s="28"/>
@@ -2811,20 +2810,20 @@
       <c r="BR47" s="26"/>
     </row>
     <row r="48" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="BE48" s="14"/>
-      <c r="BF48" s="15"/>
-      <c r="BG48" s="14"/>
-      <c r="BH48" s="15"/>
-      <c r="BI48" s="14"/>
-      <c r="BJ48" s="15"/>
-      <c r="BK48" s="14"/>
-      <c r="BL48" s="15"/>
-      <c r="BM48" s="14"/>
-      <c r="BN48" s="15"/>
-      <c r="BO48" s="14"/>
-      <c r="BP48" s="15"/>
-      <c r="BQ48" s="14"/>
-      <c r="BR48" s="15"/>
+      <c r="BE48" s="15"/>
+      <c r="BF48" s="16"/>
+      <c r="BG48" s="15"/>
+      <c r="BH48" s="16"/>
+      <c r="BI48" s="15"/>
+      <c r="BJ48" s="16"/>
+      <c r="BK48" s="15"/>
+      <c r="BL48" s="16"/>
+      <c r="BM48" s="15"/>
+      <c r="BN48" s="16"/>
+      <c r="BO48" s="15"/>
+      <c r="BP48" s="16"/>
+      <c r="BQ48" s="15"/>
+      <c r="BR48" s="16"/>
     </row>
     <row r="49" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="BE49" s="28"/>
@@ -3067,20 +3066,20 @@
       <c r="BR63" s="26"/>
     </row>
     <row r="64" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="BE64" s="14"/>
-      <c r="BF64" s="15"/>
-      <c r="BG64" s="14"/>
-      <c r="BH64" s="15"/>
-      <c r="BI64" s="14"/>
-      <c r="BJ64" s="15"/>
-      <c r="BK64" s="14"/>
-      <c r="BL64" s="15"/>
-      <c r="BM64" s="14"/>
-      <c r="BN64" s="15"/>
-      <c r="BO64" s="14"/>
-      <c r="BP64" s="15"/>
-      <c r="BQ64" s="14"/>
-      <c r="BR64" s="15"/>
+      <c r="BE64" s="15"/>
+      <c r="BF64" s="16"/>
+      <c r="BG64" s="15"/>
+      <c r="BH64" s="16"/>
+      <c r="BI64" s="15"/>
+      <c r="BJ64" s="16"/>
+      <c r="BK64" s="15"/>
+      <c r="BL64" s="16"/>
+      <c r="BM64" s="15"/>
+      <c r="BN64" s="16"/>
+      <c r="BO64" s="15"/>
+      <c r="BP64" s="16"/>
+      <c r="BQ64" s="15"/>
+      <c r="BR64" s="16"/>
     </row>
     <row r="65" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="BE65" s="28"/>
@@ -3323,52 +3322,52 @@
       <c r="BR79" s="26"/>
     </row>
     <row r="80" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="BE80" s="14"/>
-      <c r="BF80" s="15"/>
-      <c r="BG80" s="14"/>
-      <c r="BH80" s="15"/>
-      <c r="BI80" s="14"/>
-      <c r="BJ80" s="15"/>
-      <c r="BK80" s="14"/>
-      <c r="BL80" s="15"/>
-      <c r="BM80" s="14"/>
-      <c r="BN80" s="15"/>
-      <c r="BO80" s="14"/>
-      <c r="BP80" s="15"/>
-      <c r="BQ80" s="14"/>
-      <c r="BR80" s="15"/>
+      <c r="BE80" s="15"/>
+      <c r="BF80" s="16"/>
+      <c r="BG80" s="15"/>
+      <c r="BH80" s="16"/>
+      <c r="BI80" s="15"/>
+      <c r="BJ80" s="16"/>
+      <c r="BK80" s="15"/>
+      <c r="BL80" s="16"/>
+      <c r="BM80" s="15"/>
+      <c r="BN80" s="16"/>
+      <c r="BO80" s="15"/>
+      <c r="BP80" s="16"/>
+      <c r="BQ80" s="15"/>
+      <c r="BR80" s="16"/>
     </row>
     <row r="81" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="BE81" s="14"/>
-      <c r="BF81" s="15"/>
-      <c r="BG81" s="14"/>
-      <c r="BH81" s="15"/>
-      <c r="BI81" s="14"/>
-      <c r="BJ81" s="15"/>
-      <c r="BK81" s="14"/>
-      <c r="BL81" s="15"/>
-      <c r="BM81" s="14"/>
-      <c r="BN81" s="15"/>
-      <c r="BO81" s="14"/>
-      <c r="BP81" s="15"/>
-      <c r="BQ81" s="14"/>
-      <c r="BR81" s="15"/>
+      <c r="BE81" s="15"/>
+      <c r="BF81" s="16"/>
+      <c r="BG81" s="15"/>
+      <c r="BH81" s="16"/>
+      <c r="BI81" s="15"/>
+      <c r="BJ81" s="16"/>
+      <c r="BK81" s="15"/>
+      <c r="BL81" s="16"/>
+      <c r="BM81" s="15"/>
+      <c r="BN81" s="16"/>
+      <c r="BO81" s="15"/>
+      <c r="BP81" s="16"/>
+      <c r="BQ81" s="15"/>
+      <c r="BR81" s="16"/>
     </row>
     <row r="82" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="BE82" s="14"/>
-      <c r="BF82" s="15"/>
-      <c r="BG82" s="14"/>
-      <c r="BH82" s="15"/>
-      <c r="BI82" s="14"/>
-      <c r="BJ82" s="15"/>
-      <c r="BK82" s="14"/>
-      <c r="BL82" s="15"/>
-      <c r="BM82" s="14"/>
-      <c r="BN82" s="15"/>
-      <c r="BO82" s="14"/>
-      <c r="BP82" s="15"/>
-      <c r="BQ82" s="14"/>
-      <c r="BR82" s="15"/>
+      <c r="BE82" s="15"/>
+      <c r="BF82" s="16"/>
+      <c r="BG82" s="15"/>
+      <c r="BH82" s="16"/>
+      <c r="BI82" s="15"/>
+      <c r="BJ82" s="16"/>
+      <c r="BK82" s="15"/>
+      <c r="BL82" s="16"/>
+      <c r="BM82" s="15"/>
+      <c r="BN82" s="16"/>
+      <c r="BO82" s="15"/>
+      <c r="BP82" s="16"/>
+      <c r="BQ82" s="15"/>
+      <c r="BR82" s="16"/>
     </row>
   </sheetData>
   <mergeCells count="7">
